--- a/data/processed/positivacao/2024-02_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-02_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26063,7 +26063,7 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B990" t="inlineStr"/>
@@ -37311,7 +37311,7 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr"/>
@@ -65865,7 +65865,7 @@
     <row r="2522">
       <c r="A2522" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2522" t="inlineStr"/>
@@ -67536,12 +67536,12 @@
       <c r="A2587" t="inlineStr"/>
       <c r="B2587" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 7 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 11.014,69
+          <t>Vendedor 1 - VENDEDOR 01: positivou 7 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 11.014,69
 Vendedor 18 - LOJA: positivou 164 cliente(s), não positivou 721 cliente(s) - Total vendido: R$ 61.266,76
-Vendedor 3 - FERNANDA: positivou 103 cliente(s), não positivou 329 cliente(s) - Total vendido: R$ 155.458,16
-Vendedor 4 - DANIELA: positivou 84 cliente(s), não positivou 567 cliente(s) - Total vendido: R$ 45.436,66
+Vendedor 3 - VENDEDOR 03: positivou 103 cliente(s), não positivou 329 cliente(s) - Total vendido: R$ 155.458,16
+Vendedor 4 - VENDEDOR 04: positivou 84 cliente(s), não positivou 567 cliente(s) - Total vendido: R$ 45.436,66
 Vendedor 5 - SITE: positivou 4 cliente(s), não positivou 442 cliente(s) - Total vendido: R$ 789,65
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2587" t="inlineStr"/>
